--- a/光伏配储项目/电价数据/2026/祥云站.xlsx
+++ b/光伏配储项目/电价数据/2026/祥云站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.34101</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.87488</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.37629</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.40124</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.36483</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.40097</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.28538</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.26304</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.30411</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07534</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.7869700000000001</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.70639</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17311</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.26924</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25438</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.25896</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24367</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.6694600000000001</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.45909</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.30771</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29023</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6299400000000001</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.61109</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7885</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.29929</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.40782</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.76823</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.4503</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.45963</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.7024</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.00353</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.54334</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.35717</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.44624</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.21728</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.31741</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.4874</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.6272</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.51527</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.79314</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.8560599999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.33733</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.35107</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.97224</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.8787999999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.8340700000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5542699999999999</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.51448</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.49679</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.43931</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.45066</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7458899999999999</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.93879</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9993</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.50151</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52067</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.51041</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5101600000000001</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49095</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40225</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47251</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38018</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37694</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.46836</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.37227</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30512</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29909</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.46268</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.47776</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.66752</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.63166</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.81391</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.30294</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.31351</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.89698</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.6583300000000001</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.51087</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.41985</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.36743</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.6502</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.39217</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.37809</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.91934</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.60951</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.76952</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.8182</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.27769</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.745</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.25551</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.9105700000000001</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.36414</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.24081</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.43222</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.13972</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.22545</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.70192</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.08295</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.94404</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.09893</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.97446</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.19203</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.94489</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45038</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.90399</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.9311699999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44969</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42869</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44411</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3336</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.3349</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51223</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.49147</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.49575</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37454</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44851</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41632</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39145</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38497</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43143</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44747</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37198</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39849</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36892</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36293</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39415</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47731</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44639</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4415</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.3963</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.14727</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.18801</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.26976</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.36905</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.10398</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.79788</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.6565700000000001</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.64475</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.82675</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.8242999999999999</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.81937</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.8280700000000001</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.83892</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.86527</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.88075</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.00409</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.5372899999999999</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.5797100000000001</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.79269</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.79625</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.67279</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.6967899999999999</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.5188200000000001</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.76527</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.41219</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38628</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45728</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.5138200000000001</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.5229199999999999</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.59348</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.63778</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.6306900000000001</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.6501399999999999</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.2534</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.61787</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.70328</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46848</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50993</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.6216499999999999</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.75373</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.75903</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.87351</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.45849</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.64238</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.44636</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.5265700000000001</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6075199999999999</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.7774</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.5718</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.88202</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.7152000000000001</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.61042</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.55945</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.7054600000000001</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43904</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45725</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39758</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34229</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.54247</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.51995</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.45631</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39686</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39598</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.3982</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.3728</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39767</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39516</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36711</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46558</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36311</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36335</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33637</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39302</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39717</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39464</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42469</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44614</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44285</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37456</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.48676</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35322</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.61391</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.47473</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.46387</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37464</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.25831</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.28923</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.7617200000000001</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.37803</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35434</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.41129</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.59077</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31741</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.5131699999999999</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.44034</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.3959</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.36783</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.3757200000000001</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.36417</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.47511</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.6216900000000001</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.40739</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.48706</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45066</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.45447</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39796</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47185</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.55843</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.6563600000000001</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.48921</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.66495</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.5264099999999999</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.49494</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5025500000000001</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.4566</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.4343399999999999</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.41714</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41154</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31843</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37073</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37519</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.3132799999999999</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.29973</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28858</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.30388</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14288</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02415</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.31435</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.30416</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.41176</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.40591</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.27157</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.26122</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.24519</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.11098</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.06659999999999999</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26346</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30482</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34633</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36455</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.44318</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42942</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34182</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.3167</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.23769</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.24448</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.2272</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.28671</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.1893</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.28132</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.14975</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.24711</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30459</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.1693</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.24696</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.21302</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.1907</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.2724</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.17185</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30489</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.24777</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.26935</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.19904</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26637</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10219</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04322</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.009949999999999999</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20607</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.0492</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27522</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19846</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.43847</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.00996</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06022</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05843</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.34257</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31546</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30165</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32285</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.41355</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38034</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42895</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45768</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39198</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78546</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88748</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87033</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.6549199999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.57259</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45226</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42071</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39267</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37776</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38707</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39768</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37425</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44356</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.45253</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5494600000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60711</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.88471</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.45924</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.43755</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.36778</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.58548</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.82277</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.42956</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29166</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26535</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.38779</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.57243</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.42925</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30364</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28465</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29309</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29445</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30525</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.17728</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.26165</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26121</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.2761</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.26051</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.28035</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30774</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29315</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29247</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.30089</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.30842</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.30184</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.30492</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.28885</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32306</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9906</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30693</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30648</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29237</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.30071</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29581</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.31664</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.29549</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.2963</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.29615</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.29969</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.28737</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29161</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29545</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.30843</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30666</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30328</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30335</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29341</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.46734</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.39702</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.49524</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20131</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.31316</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31636</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.29413</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.27147</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.29436</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.18595</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.25821</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28507</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.27411</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.26997</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.28879</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29302</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25943</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.29036</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.28058</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.29604</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.30299</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.30038</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.28373</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31778</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.31755</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42908</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.41745</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.29983</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.30617</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.29965</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.21197</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.79406</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.45748</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.08475</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.65774</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.77195</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.61153</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.21187</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.20817</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.41964</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.47196</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43075</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.3892</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.38694</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.38347</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.40478</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.29709</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.41836</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.28672</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.28864</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.3658</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.40438</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.28979</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.38299</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38288</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.28944</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.28632</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.36784</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.28428</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.45759</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.15808</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.25823</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.26457</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.28606</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29295</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.27665</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.28243</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.41603</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.2523</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.29535</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.1458</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.26459</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.02895</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26112</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.24817</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.31135</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28511</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.26897</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.27814</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28007</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.29051</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.30023</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.29932</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.28574</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.29337</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.29707</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.27506</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.28417</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.44387</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.5760299999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.37386</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.30751</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.29246</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.26952</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.28959</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.25477</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.26864</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.25403</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.24875</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.15802</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.18426</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.18492</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.17746</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.18217</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.14897</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.23115</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.25225</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.24993</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.29052</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.28656</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.13893</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.13932</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.27057</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.28514</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.28199</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.17151</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.18411</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.19169</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.18219</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.17656</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.26606</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.22914</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.27068</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.15463</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.28673</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.29626</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.13944</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.19662</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.28523</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.27703</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.36128</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.39493</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28881</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.30212</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.29897</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.27201</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.30121</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26556</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.27374</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.29747</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.2854100000000001</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.29396</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.28044</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.29831</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30205</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30163</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.30452</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.29123</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.29146</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.29629</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.29171</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.29655</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.30226</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.29091</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.29565</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.43311</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.36505</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.28311</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.28548</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.24763</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.2802</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.28864</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.30652</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.30042</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30676</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.30388</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.29663</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29505</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.29856</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29451</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29347</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29491</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29347</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.2996</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.29935</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.29448</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.29904</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.30048</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.29014</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29412</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.30059</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30725</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28199</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28474</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28742</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28838</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.28525</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30165</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30309</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29408</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.42111</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29698</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29377</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.28886</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28947</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33378</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33426</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.41231</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.38461</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.39582</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.49013</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37867</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32361</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.33392</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.28611</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.31324</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30611</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.3132200000000001</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.28596</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29147</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28521</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.29113</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29647</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.3161600000000001</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29306</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30784</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.2924</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.30915</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30465</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29337</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29467</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.35573</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.30754</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.30816</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29453</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30314</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.43314</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.33106</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.44677</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.7697000000000001</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.41104</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.54359</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.48874</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.39696</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.47987</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.55586</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.41053</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.46724</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.38949</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.63422</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27723</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.44213</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.27256</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.37298</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.39265</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.80402</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.47857</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.40161</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.4766</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.45057</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.43568</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.6230399999999999</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.45826</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.44937</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.4955</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.4123</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.48475</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.37115</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.40128</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.3416</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.43453</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.38703</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.35781</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.68487</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.5026</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.46262</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.52224</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.44005</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.71562</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.38459</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.27561</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34385</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.48015</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.2181</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.30263</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.26168</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28347</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.19751</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30685</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.28279</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38365</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.28304</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.27699</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.27841</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.27746</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.19553</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.18788</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.27325</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.27567</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27319</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.27291</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.27298</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27289</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.18965</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29466</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.18704</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.15008</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.2334</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.28941</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.29258</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.26084</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.18678</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.19251</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.21004</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.1991</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.16285</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.15442</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.21042</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.23383</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.28752</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.30364</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.29643</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.29633</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.27322</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.29292</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.2929</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.28559</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.28995</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.25254</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.29011</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29581</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.28347</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.29739</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.29283</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.28148</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.28199</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.26423</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.27492</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.27976</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.22504</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.29146</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.36331</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.2933</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.30108</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.30236</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.29864</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.26039</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28561</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.27788</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.28553</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.27192</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.2839</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.27813</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.28709</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.23206</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.27577</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.20424</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.23193</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.31901</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.29146</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.27925</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.02459</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.28776</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28409</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27229</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.30899</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28442</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.28128</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28177</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.30901</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.28218</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28419</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27158</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31445</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28304</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.28843</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.28792</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.2791</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27293</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28263</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29182</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.27275</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28352</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.26961</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.29059</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30628</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30585</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30471</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30224</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31445</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.42274</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.67891</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.61305</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.20199</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.30903</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29567</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.38057</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31425</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31703</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.28216</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.4054</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31292</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.43199</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.37954</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.40399</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.49321</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.49736</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.72112</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6722100000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.7271799999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.8865499999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.42989</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.39485</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.53942</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.43476</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.48948</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31324</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.31942</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36419</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.30783</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.28508</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.30145</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.30878</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.29276</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.27869</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.29408</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.29035</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.30525</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.30887</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.3067</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.4484</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.42473</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.42236</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.4813</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.52459</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.5756699999999999</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.57569</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40402</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40695</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37925</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.43747</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.67503</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40615</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.90242</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39561</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.53504</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.37381</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31425</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.38058</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.40574</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.31476</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.30618</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.39727</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.81779</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6430800000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6419400000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.31291</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40394</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39388</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38561</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.31123</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.26245</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.28466</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.28877</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.30645</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30338</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.0102</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.27374</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28226</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.27353</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.28076</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.28992</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39099</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.34355</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.36892</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37631</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.3945</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.37492</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.38147</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.39147</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.41777</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.39284</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.42982</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.42978</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.42358</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.40387</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.38273</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.29106</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.30306</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.30519</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.37752</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.31174</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.21462</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.40141</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38696</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37756</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.21544</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.21162</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.23327</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.26919</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.25619</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.2214</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.2707</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.28457</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.17542</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.29302</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.16319</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.18614</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.17821</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.20539</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.1835</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.30242</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.28261</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.26292</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.22581</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.27916</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.21544</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.16251</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.01251</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.25849</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.01507</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.01448</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.16275</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.02633</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.19659</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.16154</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.01481</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.15235</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.15678</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.19253</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.15447</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.15713</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.15978</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.01521</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.16244</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.01531</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.04103</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.17309</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.17863</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.14499</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28278</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.25965</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.3161600000000001</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.28144</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.35423</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.2516</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.4595</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.31409</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.19724</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.00046</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28919</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.33645</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31181</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.36919</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27058</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.28917</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28234</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.29617</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.30255</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.24796</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.26182</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.29175</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.30461</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.28325</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.25861</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.27893</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.26998</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.2621</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.21566</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.22983</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.21127</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.24251</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.25743</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.29199</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.25232</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.24919</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.1693</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.17669</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.25241</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.15812</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.27458</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.15801</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.22732</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.28761</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.27763</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.27591</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.28054</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.2713</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.03382</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.18109</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.17817</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26562</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.02007</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.19997</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.22119</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.21276</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.02584</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.03187</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.01782</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.01783</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.01818</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.01818</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.01797</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.1946</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.03211</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.01818</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.01815</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.17319</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.03187</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.03186</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30408</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.01711</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.01633</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24395</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.02328</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.007730000000000001</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00037</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14362</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02206</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01579</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04298</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.0409</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02936</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04367</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00044</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27556</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04931</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03799</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02081</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03621</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20097</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26538</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28825</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.2787</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.27916</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.28964</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.01723</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.28726</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.30306</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28039</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30655</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.29337</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29505</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30323</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.2914</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29831</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.26774</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.31709</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.29712</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.27577</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.30135</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.2815299999999999</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.27711</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.16588</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.16106</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.16535</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.16277</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.04379</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.15891</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.04431</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.04348</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.01285</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.01141</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.00895</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41431</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.18945</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27492</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.23285</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.30648</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85746</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8621599999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09067</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.01462</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.24776</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31384</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28126</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29546</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29327</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.5174299999999999</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.30039</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29364</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00247</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29293</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00175</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31377</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06916</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30816</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30267</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30822</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25453</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47524</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.7899299999999999</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.5837100000000001</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.38738</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.45609</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.92749</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.07022</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.40057</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.67614</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.4692</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.90464</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.90287</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.9079700000000001</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.02252</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.38539</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.46698</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.39897</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.30648</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.33405</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.49574</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.30323</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.28818</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.26781</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.2619</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.18732</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.25738</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.25203</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.24547</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.21285</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.25343</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.19947</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.1638</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.1951</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.15839</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.16103</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.04431</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.15378</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.17834</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.22897</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.27661</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.23757</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.24661</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29712</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.25072</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.27409</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.30207</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37896</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.29896</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.28616</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.3092200000000001</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30719</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31583</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30859</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25859</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30245</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31734</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.39831</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.36302</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39688</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.31589</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.30585</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.2944</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.28908</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.28992</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36985</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.36224</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.31174</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29292</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29675</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.29899</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.29907</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30592</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.30118</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.64047</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.46058</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.31671</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.36188</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29591</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.3336</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.48987</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.43845</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.49687</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.20732</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.90425</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.9341</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.42969</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.42632</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5772999999999999</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.77867</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.95394</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.43577</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.65992</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42483</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.19972</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.30645</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31536</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.41339</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30408</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.2985</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.29646</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29234</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.29176</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.3027</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.30585</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35365</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43458</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37965</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35428</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.37735</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.36293</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.35528</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.38616</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.4099100000000001</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.39189</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5853400000000001</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.61319</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.41385</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.98726</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.6552899999999999</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.89725</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.5406599999999999</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.69177</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.6043200000000001</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.47347</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.86286</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.7850499999999999</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.33032</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.93953</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.80448</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.66098</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.43201</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.31997</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28333</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.28242</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.29411</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.28786</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.28903</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.30329</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.29986</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30062</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.0476</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.28682</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.28765</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.28194</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.28871</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.27974</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35621</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33392</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30351</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30192</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.30603</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32979</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.35472</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.37674</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.26826</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.42903</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.55622</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19947</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29815</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43541</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.5263099999999999</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.39171</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.48029</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36599</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.46917</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.33405</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.40979</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.51908</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.41661</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.49756</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.43006</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.51351</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.6616799999999999</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.42247</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.5327499999999999</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.44285</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.46545</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.32388</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.80402</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.42282</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.49416</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.44142</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.38158</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33416</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36074</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.30878</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.38317</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.30162</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.27351</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.41546</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.5036499999999999</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30361</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35377</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.40959</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.42142</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42838</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.42216</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.42578</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38718</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.36576</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.47407</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.5902200000000001</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.46086</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.46463</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.41178</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.3367</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.38193</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.30318</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37215</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30481</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17612</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.2958</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14578</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19869</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14679</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28733</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04802</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12185</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22641</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26019</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14333</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14563</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28357</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22688</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27077</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15833</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36273</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.1668</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30145</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20181</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.17578</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.29665</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.39335</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.37165</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.46094</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.38702</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.39443</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.3903</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.44287</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.46503</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.39569</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.25463</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.42625</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.41321</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.36899</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.41243</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.42091</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.45497</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39968</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39024</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38605</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.36307</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.36382</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36755</v>
       </c>
     </row>
   </sheetData>
